--- a/kaufpunkte_leer.xlsx
+++ b/kaufpunkte_leer.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:BI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,38 @@
     <col width="9" customWidth="1" min="26" max="26"/>
     <col width="9" customWidth="1" min="27" max="27"/>
     <col width="30" customWidth="1" min="28" max="28"/>
-    <col width="60" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="11" customWidth="1" min="37" max="37"/>
+    <col width="11" customWidth="1" min="38" max="38"/>
+    <col width="11" customWidth="1" min="39" max="39"/>
+    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="11" customWidth="1" min="41" max="41"/>
+    <col width="11" customWidth="1" min="42" max="42"/>
+    <col width="11" customWidth="1" min="43" max="43"/>
+    <col width="11" customWidth="1" min="44" max="44"/>
+    <col width="11" customWidth="1" min="45" max="45"/>
+    <col width="11" customWidth="1" min="46" max="46"/>
+    <col width="11" customWidth="1" min="47" max="47"/>
+    <col width="11" customWidth="1" min="48" max="48"/>
+    <col width="11" customWidth="1" min="49" max="49"/>
+    <col width="11" customWidth="1" min="50" max="50"/>
+    <col width="11" customWidth="1" min="51" max="51"/>
+    <col width="11" customWidth="1" min="52" max="52"/>
+    <col width="11" customWidth="1" min="53" max="53"/>
+    <col width="11" customWidth="1" min="54" max="54"/>
+    <col width="11" customWidth="1" min="55" max="55"/>
+    <col width="11" customWidth="1" min="56" max="56"/>
+    <col width="11" customWidth="1" min="57" max="57"/>
+    <col width="11" customWidth="1" min="58" max="58"/>
+    <col width="11" customWidth="1" min="59" max="59"/>
+    <col width="60" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -626,6 +657,161 @@
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ADR 20 %</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Volatilität Woche %</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Volatilität Monat %</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ATR 14 %</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Up/Down-Vol. 50</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Mansfield RS</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Weinstein-Stufe</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Momentum Burst</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Lücke %</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Episodic Pivot</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Perf. 1W %</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Perf. 1M %</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Perf. 3M %</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Perf. 6M %</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Perf. 12M %</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>Perf. lfd. Jahr %</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Abst. SMA20 %</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Abst. SMA50 %</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Abst. SMA200 %</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Abst. 50T-Hoch %</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Abst. 50T-Tief %</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Abst. 52W-Tief %</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Allzeithoch</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Abst. Allzeithoch %</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>RSI 14</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>RSI 2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Vol. 3M</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>Dollarvol. 20T</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>RS Änd. 1W</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>RS Änd. 4W</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Notizen</t>
         </is>
@@ -642,7 +828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -709,6 +895,18 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kennzahlen</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Spalten von ADR 20 bis RS Änd. 4W: technische Kennzahlen aus den Tageskursen, Entscheidungshilfen, reine Anzeige, keine davon filtert (Gerhard, 13.09.2026). Prozentwerte in Prozentpunkten; Allzeithoch aus der ganzen Kurshistorie; Weinstein-Stufe nach festen Regeln</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kaufpunkte_leer.xlsx
+++ b/kaufpunkte_leer.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>Beta</t>
+          <t>Beta 252T</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -883,6 +883,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -903,7 +904,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Spalten von ADR 20 bis RS Änd. 4W: technische Kennzahlen aus den Tageskursen, Entscheidungshilfen, reine Anzeige, keine davon filtert (Gerhard, 13.09.2026). Prozentwerte in Prozentpunkten; Allzeithoch aus der ganzen Kurshistorie; Weinstein-Stufe nach festen Regeln</t>
+          <t>Spalten von ADR 20 bis RS Änd. 4W: technische Kennzahlen aus den Tageskursen, Entscheidungshilfen, reine Anzeige, keine davon filtert (Gerhard, 13.09.2026). Prozentwerte in Prozentpunkten; Allzeithoch aus der ganzen Kurshistorie; Weinstein-Stufe nach festen Regeln aus 30-Wochen-Linie und Kurs; Beta 252T gegen SPY über 252 Handelstage</t>
         </is>
       </c>
     </row>
